--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/IS381 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FACD12F-BA64-944C-B4B9-CB1F7C74E082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E0A5A8-8603-D149-B886-45078AEF03AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="3240" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>Week</t>
   </si>
@@ -210,6 +210,9 @@
   </si>
   <si>
     <t>pwFIHg-dK68</t>
+  </si>
+  <si>
+    <t>04-Data_Visualization</t>
   </si>
 </sst>
 </file>
@@ -1255,6 +1258,9 @@
       <c r="G5" t="s">
         <v>24</v>
       </c>
+      <c r="H5" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/IS381 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E0A5A8-8603-D149-B886-45078AEF03AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2C9148-711F-2043-8F99-EB54FC6C1AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="3240" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>Week</t>
   </si>
@@ -213,6 +213,9 @@
   </si>
   <si>
     <t>04-Data_Visualization</t>
+  </si>
+  <si>
+    <t>qijGZYiMoSE</t>
   </si>
 </sst>
 </file>
@@ -1261,6 +1264,9 @@
       <c r="H5" t="s">
         <v>59</v>
       </c>
+      <c r="I5" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/IS381 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2C9148-711F-2043-8F99-EB54FC6C1AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C469A13-575C-164F-AB40-CA7DC4E2D53A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="3240" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
+    <workbookView xWindow="1780" yWindow="8220" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>Week</t>
   </si>
@@ -216,6 +216,12 @@
   </si>
   <si>
     <t>qijGZYiMoSE</t>
+  </si>
+  <si>
+    <t>05-Reshaping_Data</t>
+  </si>
+  <si>
+    <t>FnYPi9XN4DA</t>
   </si>
 </sst>
 </file>
@@ -1293,6 +1299,12 @@
       <c r="G6" t="s">
         <v>25</v>
       </c>
+      <c r="H6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/IS381 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C469A13-575C-164F-AB40-CA7DC4E2D53A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC0012AE-7F24-E044-AE44-2D1D1A079F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1780" yWindow="8220" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>Week</t>
   </si>
@@ -222,6 +222,12 @@
   </si>
   <si>
     <t>FnYPi9XN4DA</t>
+  </si>
+  <si>
+    <t>3A3rEnGl30k</t>
+  </si>
+  <si>
+    <t>06-Probabilty</t>
   </si>
 </sst>
 </file>
@@ -1331,6 +1337,12 @@
       <c r="G7" t="s">
         <v>26</v>
       </c>
+      <c r="H7" t="s">
+        <v>64</v>
+      </c>
+      <c r="I7" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/IS381 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC0012AE-7F24-E044-AE44-2D1D1A079F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88038011-49E4-7C4F-89AB-4E6EFB785008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1780" yWindow="8220" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
+    <workbookView xWindow="14720" yWindow="8840" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t>Week</t>
   </si>
@@ -228,6 +228,12 @@
   </si>
   <si>
     <t>06-Probabilty</t>
+  </si>
+  <si>
+    <t>YeY-5yfrLVE</t>
+  </si>
+  <si>
+    <t>07-Distributions</t>
   </si>
 </sst>
 </file>
@@ -1369,6 +1375,12 @@
       <c r="G8" t="s">
         <v>27</v>
       </c>
+      <c r="H8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/IS381 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88038011-49E4-7C4F-89AB-4E6EFB785008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0348CF8E-D307-6343-85DF-9FBCB6AEC498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14720" yWindow="8840" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
+    <workbookView xWindow="1780" yWindow="13680" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>Week</t>
   </si>
@@ -56,9 +56,6 @@
     <t>Foundation for inference</t>
   </si>
   <si>
-    <t>Central limit theorem</t>
-  </si>
-  <si>
     <t>Inference for proportions</t>
   </si>
   <si>
@@ -234,6 +231,15 @@
   </si>
   <si>
     <t>07-Distributions</t>
+  </si>
+  <si>
+    <t>Null Hypothesis Testing</t>
+  </si>
+  <si>
+    <t>08-Foundation_for_Inference</t>
+  </si>
+  <si>
+    <t>S-dUZRl59rk</t>
   </si>
 </sst>
 </file>
@@ -1145,25 +1151,25 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>15</v>
       </c>
-      <c r="I1" t="s">
-        <v>16</v>
-      </c>
       <c r="J1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -1184,16 +1190,16 @@
         <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" t="s">
         <v>54</v>
-      </c>
-      <c r="I2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1213,19 +1219,19 @@
         <v>45901</v>
       </c>
       <c r="E3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
         <v>56</v>
       </c>
-      <c r="F3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -1248,10 +1254,10 @@
         <v>4</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1274,16 +1280,16 @@
         <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" t="s">
         <v>59</v>
-      </c>
-      <c r="I5" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -1303,19 +1309,19 @@
         <v>45922</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" t="s">
         <v>61</v>
-      </c>
-      <c r="I6" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1335,19 +1341,19 @@
         <v>45929</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1367,19 +1373,19 @@
         <v>45936</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1402,10 +1408,16 @@
         <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="H9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1425,13 +1437,13 @@
         <v>45950</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -1451,13 +1463,13 @@
         <v>45957</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -1477,13 +1489,13 @@
         <v>45964</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -1503,13 +1515,13 @@
         <v>45971</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1529,13 +1541,13 @@
         <v>45978</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -1548,7 +1560,7 @@
         <v>45991</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -1567,13 +1579,13 @@
         <v>45992</v>
       </c>
       <c r="E16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -1593,10 +1605,10 @@
         <v>45999</v>
       </c>
       <c r="E17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/IS381 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0348CF8E-D307-6343-85DF-9FBCB6AEC498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2B3453-4102-5848-AD9C-E1B20B220FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1780" yWindow="13680" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>Week</t>
   </si>
@@ -240,6 +240,12 @@
   </si>
   <si>
     <t>S-dUZRl59rk</t>
+  </si>
+  <si>
+    <t>09-CLT_and_Bootstrapping</t>
+  </si>
+  <si>
+    <t>O8HOuwEJ228</t>
   </si>
 </sst>
 </file>
@@ -1445,6 +1451,12 @@
       <c r="G10" t="s">
         <v>28</v>
       </c>
+      <c r="H10" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/IS381 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2B3453-4102-5848-AD9C-E1B20B220FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504DF1B8-CA4A-474F-8261-B0962682D46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1780" yWindow="13680" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
   <si>
     <t>Week</t>
   </si>
@@ -246,6 +246,12 @@
   </si>
   <si>
     <t>O8HOuwEJ228</t>
+  </si>
+  <si>
+    <t>10-Inference_for_Proportions</t>
+  </si>
+  <si>
+    <t>zxF_F0rsHgM</t>
   </si>
 </sst>
 </file>
@@ -1483,6 +1489,12 @@
       <c r="G11" t="s">
         <v>29</v>
       </c>
+      <c r="H11" t="s">
+        <v>71</v>
+      </c>
+      <c r="I11" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/IS381 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504DF1B8-CA4A-474F-8261-B0962682D46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8F2921-2439-9146-852A-2FC15D5471C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1780" yWindow="13680" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <si>
     <t>Week</t>
   </si>
@@ -252,6 +252,12 @@
   </si>
   <si>
     <t>zxF_F0rsHgM</t>
+  </si>
+  <si>
+    <t>11-Inference_for_Proportions</t>
+  </si>
+  <si>
+    <t>_6f3EKHuiig</t>
   </si>
 </sst>
 </file>
@@ -1521,6 +1527,12 @@
       <c r="G12" t="s">
         <v>30</v>
       </c>
+      <c r="H12" t="s">
+        <v>73</v>
+      </c>
+      <c r="I12" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/IS381 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8F2921-2439-9146-852A-2FC15D5471C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1EBE56D-E4EF-1145-AE5F-9D92D6A19C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1780" yWindow="13680" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>Week</t>
   </si>
@@ -258,6 +258,12 @@
   </si>
   <si>
     <t>_6f3EKHuiig</t>
+  </si>
+  <si>
+    <t>12-Inference_for_Numerical_Data</t>
+  </si>
+  <si>
+    <t>LZDkij5cQxQ</t>
   </si>
 </sst>
 </file>
@@ -1559,6 +1565,12 @@
       <c r="G13" t="s">
         <v>31</v>
       </c>
+      <c r="H13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/IS381 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1EBE56D-E4EF-1145-AE5F-9D92D6A19C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82AFFFAF-41CE-984B-8BF1-763C0C83D0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1780" yWindow="13680" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>Week</t>
   </si>
@@ -264,6 +264,12 @@
   </si>
   <si>
     <t>LZDkij5cQxQ</t>
+  </si>
+  <si>
+    <t>13-ANOVA</t>
+  </si>
+  <si>
+    <t>lUo4uWGHJU8</t>
   </si>
 </sst>
 </file>
@@ -1597,6 +1603,12 @@
       <c r="G14" t="s">
         <v>32</v>
       </c>
+      <c r="H14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I14" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B15" s="3">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/IS381 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82AFFFAF-41CE-984B-8BF1-763C0C83D0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EDA579-7000-1A44-A691-A1AF09727BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1780" yWindow="13680" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t>Week</t>
   </si>
@@ -270,6 +270,12 @@
   </si>
   <si>
     <t>lUo4uWGHJU8</t>
+  </si>
+  <si>
+    <t>14-Correlation</t>
+  </si>
+  <si>
+    <t>bv_zlhbCdag</t>
   </si>
 </sst>
 </file>
@@ -1647,6 +1653,12 @@
       <c r="G16" t="s">
         <v>33</v>
       </c>
+      <c r="H16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
